--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5198.</t>
+          <t>5322.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5094.</t>
+          <t>5218.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1656.</t>
+          <t>1786.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3848.</t>
+          <t>3976.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4070.</t>
+          <t>4197.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4094.</t>
+          <t>4221.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5248.</t>
+          <t>5372.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2700.</t>
+          <t>2829.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5322.</t>
+          <t>5474.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5218.</t>
+          <t>5375.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1786.</t>
+          <t>2370.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3976.</t>
+          <t>4404.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4197.</t>
+          <t>4566.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4221.</t>
+          <t>4577.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5372.</t>
+          <t>5517.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2829.</t>
+          <t>3378.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,455 +490,49 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5474.</t>
+          <t>661.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>3,44,40,000</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10000000</v>
+        <v>34440000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5375.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>21-May-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>23-Jun-2026 02:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 02:00 PM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1,34,50,000</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>13450000</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2370.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>10-Jun-2026 04:50 PM</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>03-Jul-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Medical and Health</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4404.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 05:05 PM</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4566.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 10:00 AM</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>23-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4577.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>23-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5517.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>08-May-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>18-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3378.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
         </is>
       </c>
     </row>

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>661.</t>
+          <t>1332.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,49 +490,513 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5771.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>14-May-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1,00,00,000</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>32</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1332.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2555.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>3,44,40,000</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>34440000</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5692.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21-May-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,34,50,000</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>13450000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4589.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10-Jun-2026 04:50 PM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Medical and Health</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5346.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 05:05 PM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5385.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5391.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5801.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>08-May-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5142.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>08-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,48,00,000</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>44800000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
         </is>
       </c>
     </row>

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5771.</t>
+          <t>5785.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2555.</t>
+          <t>2594.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5692.</t>
+          <t>5708.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4589.</t>
+          <t>4623.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5346.</t>
+          <t>5371.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5385.</t>
+          <t>5410.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5391.</t>
+          <t>5416.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5801.</t>
+          <t>5815.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5142.</t>
+          <t>5171.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5785.</t>
+          <t>5986.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,49 +548,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2594.</t>
+          <t>5906.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19-Jun-2026 06:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3,44,40,000</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>34440000</v>
+        <v>13450000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -606,49 +606,49 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5708.</t>
+          <t>4964.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>10-Jun-2026 04:50 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Medical and Health</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13450000</v>
+        <v>50000000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -668,32 +668,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4623.</t>
+          <t>5586.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>04-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -726,27 +726,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5371.</t>
+          <t>5613.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>04-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>23-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5410.</t>
+          <t>5619.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>04-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -842,27 +842,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5416.</t>
+          <t>6015.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>08-May-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -900,27 +900,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5815.</t>
+          <t>5401.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>08-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>29-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -930,71 +930,13 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>4,48,00,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>50000000</v>
+        <v>44800000</v>
       </c>
       <c r="L9" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>10</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5171.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
         </is>

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5986.</t>
+          <t>6018.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5906.</t>
+          <t>5938.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4964.</t>
+          <t>4996.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5586.</t>
+          <t>5618.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5613.</t>
+          <t>5645.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5619.</t>
+          <t>5651.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6015.</t>
+          <t>6047.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5401.</t>
+          <t>5433.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6018.</t>
+          <t>6162.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5938.</t>
+          <t>6082.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4996.</t>
+          <t>5317.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5618.</t>
+          <t>5809.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5645.</t>
+          <t>5836.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5651.</t>
+          <t>5842.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6047.</t>
+          <t>6191.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5433.</t>
+          <t>5679.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6162.</t>
+          <t>5975.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6082.</t>
+          <t>5898.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5317.</t>
+          <t>5220.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5809.</t>
+          <t>5656.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5836.</t>
+          <t>5682.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5842.</t>
+          <t>5688.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6191.</t>
+          <t>6003.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5679.</t>
+          <t>5538.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5975.</t>
+          <t>5612.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5898.</t>
+          <t>5552.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5220.</t>
+          <t>5059.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5656.</t>
+          <t>5375.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5682.</t>
+          <t>5389.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5688.</t>
+          <t>5395.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6003.</t>
+          <t>5641.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5538.</t>
+          <t>5286.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,52 +494,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5612.</t>
+          <t>82.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>03-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Const of covered auction platfarm 230ftx80ft by Self Supporting Metallic roofing front side of office building at Kums Pratapgarh] [RSAMB/BHILWARA/NIB NO 06/2026-27 ][2026_RSAMB_571264_12]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Ajmer||Ex.En. - Chittorgarh</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,59,20,000</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10000000</v>
+        <v>15920000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST2YIs%2B7rDVdRUX8DbBYeDA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,31 +548,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5552.</t>
+          <t>4863.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>03-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -582,22 +582,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13450000</v>
+        <v>10000000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5059.</t>
+          <t>683.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>25-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -625,30 +625,30 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,39,27,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>50000000</v>
+        <v>13927000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -664,49 +664,49 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5375.</t>
+          <t>4807.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>50000000</v>
+        <v>13450000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -726,27 +726,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5389.</t>
+          <t>47.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>15-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>16-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 11/2026-27 of EE M and Jodhpur][2026_MEDIC_570931_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SH1I9Tmt7tSMrYmTE2Aq0ow%3D%3D</t>
         </is>
       </c>
     </row>
@@ -784,27 +784,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5395.</t>
+          <t>205.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 06:15 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>12-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>13-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur (Civil, Sanitary, Joinery works)] [NIT No.03/2026-27 EE M and H DivBharatpur/][2026_MEDIC_571221_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si%2FvDRgEcsjwlBatNiPx9XA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -842,27 +842,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5641.</t>
+          <t>1297.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>23-Jun-2026 04:20 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>15-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>16-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Rate Contract for Electric Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur ] [NIT No.05/2026-27 EE M and H DivBharatpur/][2026_MEDIC_570559_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Shv4Y3gc9rnanMu%2BlPBC1%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -900,43 +900,217 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5286.</t>
+          <t>4492.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>10-Jun-2026 04:50 PM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Medical and Health</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4674.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 05:05 PM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4889.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>08-May-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4618.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>08-Jun-2026 04:00 PM</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>29-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>4,48,00,000</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K12" t="n">
         <v>44800000</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
         </is>

--- a/rajasthan_eprocurement.xlsx
+++ b/rajasthan_eprocurement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -490,11 +490,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>82.</t>
+          <t>1766.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,36 +548,36 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4863.</t>
+          <t>1548.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>26-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01-Jul-2026 02:00 PM</t>
+          <t>03-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>03-Jul-2026 04:00 PM</t>
+          <t>06-Jul-2026 11:15 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of sub division office building at Jalsu, Jaipur.] [E-NIT 02/2026-27][2026_JVVNL_571333_21]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>JVVNL - CMD||CE(O and M), Jaipur||SE-Civil</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,14 +590,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SlitjipCXcMe89SOZqYq2oQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -606,56 +606,56 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>683.</t>
+          <t>295.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25-Jun-2026 09:00 AM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
+          <t>[Construction of Police Station Building at Savina in district Udaipur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_4]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,39,27,000</t>
+          <t>3,11,00,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13927000</v>
+        <v>31100000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLIOzXMySdAgtJmxjwwPIeA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,56 +664,56 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4807.</t>
+          <t>294.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01-Jul-2026 02:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>03-Jul-2026 02:00 PM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Construction of Police station Building at Sadar Bazar under Police Commissionerate Jodhpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_3]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>3,10,24,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13450000</v>
+        <v>31024000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SR7Njsl%2FDbjyCmTu9Cl1t2g%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,56 +722,56 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.</t>
+          <t>298.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 11/2026-27 of EE M and Jodhpur][2026_MEDIC_570931_1]</t>
+          <t>[Construction of Police station building at Obri Distt Dungarpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_5]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>3,06,80,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>50000000</v>
+        <v>30680000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SH1I9Tmt7tSMrYmTE2Aq0ow%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SZsTEje51qysdt9eVkLvAaA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,56 +780,56 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>205.</t>
+          <t>299.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:15 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur (Civil, Sanitary, Joinery works)] [NIT No.03/2026-27 EE M and H DivBharatpur/][2026_MEDIC_571221_1]</t>
+          <t>[Construction of Police station building at Januthar Distt Deeg. ] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_6]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>3,05,74,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>50000000</v>
+        <v>30574000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si%2FvDRgEcsjwlBatNiPx9XA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SeiwOPN0Q9AfFa4q0d0HBcw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -838,56 +838,56 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1297.</t>
+          <t>300.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23-Jun-2026 04:20 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>16-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Rate Contract for Electric Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur ] [NIT No.05/2026-27 EE M and H DivBharatpur/][2026_MEDIC_570559_1]</t>
+          <t>[Construction of Police station Building at Chourashi in district Dungarpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_7]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>3,05,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>50000000</v>
+        <v>30500000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Shv4Y3gc9rnanMu%2BlPBC1%2FA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SAiilRqcj30%2BVXlFHowIJsQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -896,56 +896,56 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4492.</t>
+          <t>301.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Remaining work for construction of Police Station Building at Pahari Disttt. Bharatpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_8]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,76,65,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>50000000</v>
+        <v>17665000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SivrN%2B%2BGQc4lszerKDwzJCA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -954,56 +954,56 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4674.</t>
+          <t>302.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29-Jun-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30-Jun-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Remaining work of Police station Building at Itawa in district Kota] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_9]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,67,35,000</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>50000000</v>
+        <v>16735000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SISTXtJy2gLusBA%2FoSCGfVg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1012,107 +1012,1151 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4889.</t>
+          <t>3898.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>06-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>09-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Construction work for the Fire Station and Garage Wing of the Bundi Municipal Council.] [NPB/Nirman/2026-27/3144 Dated 05/06/2026][2026_DLB_567746_3]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>DLB||Dy.DR-Kota||Commissioner-Bundi</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>10,93,04,000</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>50000000</v>
+        <v>109304000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SOcbSjzEC3BXIQm3Q51hqtQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4187.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20-May-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[Neurovascular Intervention Implant for Neurosurgery Department] [1377_19.05.2026][2026_SMSMC_560591_1]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10,00,00,000</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SCH1R%2FLkR%2BnUKTAurOmciqg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3892.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[Construction of Govt. ITI Building (4 Trade) at Bardod, Distt. Kotputli-Behror] [RSAMB/Alwar/NIT-07/2026-27(1)][2026_RSAMB_567646_1]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Jaipur||Ex.En. - Alwar</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7,43,29,000</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>74329000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMcp3WJpJVJkSxOx6W8N2gw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>25.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[MRI, CT Scan and X-ray films for Radiodiagnosis dept.] [06/2026-27][2026_GMCK_572227_1]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5,68,00,000</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>56800000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S5lOBWFRPRjKrz8WUhp%2B1Mw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1072.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[Mechanized Cleaning and Senitation Services] [mechanized cleaning and sanitation service ][2026_SNMCJ_571544_1]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Dr. S.N.Medical College, Jodhpur||Principal-and-Controller||Superintendent- Umed Hospital</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5,25,00,000</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S18rI9ojqNkY1Cda93%2BNNpA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3051.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[Security Guard Skilled worker Tender for RNT Medical College and Attached Hospitals for One Year] [1387][2026_RNTMC_570234_2]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RNT Medical College, Udaipur||Principal and Controller.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2BvYNLR0%2BmxX%2FgWsG0t4ZyA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1949.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>31-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[Miscellaneous Items for HPB and Liver Transplant Surgery OT] [1711_24.06.2026][2026_SMSMC_571079_1]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4,25,00,000</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SgnhV0AOaF30etap8FNepJA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>946.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>31-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[neurosurgery items consumable, proprietory,implants tender] [436][2026_GMCK_571795_1]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller||Superintendent, Super Speciality Hospital Kota</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3,45,00,000</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SVY8L16B%2B9sz39EznSAOBBA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>293.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[Construction of administratve block of Police Station Aakola at Distt. Chittorgarh] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_2]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3,16,40,000</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>31640000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMXLsU4fDnpy8pNfYftL3Kw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4156.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>29-May-2026 05:30 PM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[Construction Work of Library and Co-Working Station Building in Sawai Madhopur] [E-NIT No. 04/2026-27 UIT Sawai Madhopur ][2026_UITSM_563395_1]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>UIT - SAWAI MADHOPUR||SECRETARY||EXECUTIVE ENGINEER</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3,00,00,000</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sh38dQxKdtdyvKhLKMX7nAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4199.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>15-May-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[Surgical And Suture Items Tender] [212][2026_GMCK_559661_1]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller||Superintendent, Super Speciality Hospital Kota</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2,12,00,000</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>21200000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScbrvXhGmoKQgtGAXfYxdKA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2256.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[Construction of New PHC Building at Burja (Block Malakhera) Distt. Alwar] [NIT NO. 07/2026-27(21)eemhalwar][2026_MEDIC_570999_1]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1,40,00,000</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SyQosoh%2FL1WEJUv%2FKgXTnAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1050.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[Miscellaneous balance civil works of Plant and Non plant buildings at SSCTPS Suratgarh] [TN/STPS-SC/2026-27/290(Civil)][2026_RRVUN_570745_1]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>RRVUN - CMD||RVUN-CE (STPS-SC) SURATGARH</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1,10,71,370</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>11071370</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SospqnumSIEQgOinMxutOlQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3068.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[4k ICG Laparoscopic Endovision System] [1382][2026_RNTMC_570127_1]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RNT Medical College, Udaipur||Principal and Controller.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1,00,00,000</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0kcBOnrt7Ree4DBm7tOGng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>32</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2248.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1,39,27,000</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>13927000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Captured Backup</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4618.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3277.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[Tender for the Procurement of Fully Automated immunodiagnostic system based on latest chemiluminesnce techniques on Reagents Rental Method] [1540_08.06.2026][2026_SMSMC_569861_1]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>11,00,00,000</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMx%2BQuPJrlNv%2FkvBqo5PTXg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4228.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>17-Apr-2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[Procurement of Gauge and Bandage for 02 years] [ENIB No 04 (2026-27)][2026_SPMCB_552196_1]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>S.P. Medical college, Bikaner||Principal, S.P.M.C., Bikaner||PBM A.G. HOSPITALS||SUPERINTENDENT</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Syw4F6SBZFGttK1HzsqKdgA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3308.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[Purchase of desktop computer] [17/2267-73 Dated- 16/06/2026][2026_SMSMC_569061_1]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1,96,59,000</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>19659000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SnCYS0i0gD4QMesbx3OsNAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3320.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[Purchase of Echo machine with TEE machine for CTVS department] [28/2267-73 Dated- 16/06/2026][2026_SMSMC_569513_1]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1,55,00,000</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SDNIOm79HSPSzlXWxxPk90g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2516.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[Package 01/2026-27/Construction of Various Development works/Bus stand Building/CC Road/Toilet Block at RSRTC Hanumangarh Depot Distt Hanumangarh. ] [EE-RSAMB-HMH-NIT-06-2026-27][2026_RSAMB_570289_1]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle SGNR||Ex.En. - Sriganganagar</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1,36,37,000</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>13637000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Svv%2BeP0mqARZt1Jkx%2BRZgig%3D%3D</t>
         </is>
       </c>
     </row>
